--- a/quizzes/003_enzymes_and_carbohydrates_quiz--quizzes.xlsx
+++ b/quizzes/003_enzymes_and_carbohydrates_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>quiz_start</t>
+          <t>enzyme_function</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Start Quiz</t>
+          <t>What is the function of enzymes?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>energy_source</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is the function of enzymes?</t>
+          <t>What is the main source of energy for the human body?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>carbohydrates_role</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What is the role of carbohydrates in the diet?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>carbohydrate_storage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the main source of energy for the human body?</t>
+          <t>How do the body store carbohydrates?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>digestion_process</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What happens to carbohydrate-rich foods when they are digested?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>high_carb_foods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the role of carbohydrates in the diet?</t>
+          <t>Which of the following foods are high in carbohydrates?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>fiber_purpose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What is the main purpose of fiber in the diet?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>high_carb_effect</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How does the body store carbohydrates?</t>
+          <t>What is the effect of a high-carbohydrate diet on the body?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>metabolism_diff</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>How does carbohydrate metabolism differ from fat and protein metabolism?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>ketosis_effect</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What happens to carbohydrate-rich foods when they are digested?</t>
+          <t>What happens to the body when it is in ketosis?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>low_carb_vs_low_fat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>What is the difference between a low-carb diet and a low-fat diet?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>low_carb_benefits</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Which of the following foods are high in carbohydrates?</t>
+          <t>What are some benefits of a low-carb diet?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>answer_6</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What is the main purpose of fiber in the diet?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>answer_7</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is the effect of a high-carbohydrate diet on the body?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>answer_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How does carbohydrate metabolism differ from fat and protein metabolism?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>answer_9</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What happens to the body when it is in ketosis?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>answer_10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the difference between a low-carb diet and a low-fat diet?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>answer_11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What are some benefits of a low-carb diet?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>answer_12</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>answer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>high_carb_foods_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>high_carb_foods_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>high_carb_foods_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1171,57 +872,6 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Carrot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>rice</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>answer_6_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>pizza</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pizza</t>
         </is>
       </c>
     </row>
